--- a/data/intermediate/fumigatus_kegg.xlsx
+++ b/data/intermediate/fumigatus_kegg.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="342">
   <si>
     <t xml:space="preserve">NAME</t>
   </si>
@@ -230,817 +230,814 @@
     <t xml:space="preserve">C00127</t>
   </si>
   <si>
+    <t xml:space="preserve">UDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDP-N-acetyl-D-glucosamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coenzyme A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acetyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-adenosyl-L-methionine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-acyl-sn-glycerol 3-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP-mannose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP-4-dehydro-6-deoxy-alpha-D-mannose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dolichyl diphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acylglycerone phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chitin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-3-methyl-2-oxobutanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fatty acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2S)-2-hydroxycarboxylate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-Oxo acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-Acylglycerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C02112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,3-dihydroxy-2,3-dihydrobenzoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5'-adenylyl sulfate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sulfate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(1),P(4)-bis(5'-adenosyl) tetraphosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isochorismate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2-Diacyl-sn-glycerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B00002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-Acetyl-D-glucosaminide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">digalacturonate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C02273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choline phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">serotonin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-Methyltetrahydrofolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-methoxytryptamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menaquinone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-S-Glutathione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C02320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dolichyl phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein asparagine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolichyl diphosphooligosaccharide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycoprotein with the oligosaccharide chain attached by N-glycosyl linkage to protein L-asparagine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Alkyl-sn-glycero-3-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-alkylglycerone phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-2,3-dihydroxy-3-methylbutanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-Acetyl-D-glucosaminyldiphosphodolichol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N,N'-diacetylchitobiosyldiphosphodolichol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demethylmenaquinone-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-hydroxy-3-methyl-2-oxobutanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Nitronaphthalene-7,8-oxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Nitro-7-glutathionyl-8-hydroxy-7,8-dihydronaphthalene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Nitronaphthalene-5,6-oxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Nitro-5-hydroxy-6-glutathionyl-5,6-dihydronaphthalene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bromobenzene-2,3-epoxide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,3-Dihydro-2-S-glutathionyl-3-hydroxy bromobenzene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benzo[a]pyrene-7,8-dihydrodiol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,8-Dihydro-7-hydroxy-8-S-glutathionyl-benzo[a]pyrene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chloroacetyl chloride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-(2-Chloroacetyl)glutathione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C06790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCVG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2-dibromoethane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glutathione episulfonium ion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrogen bromide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-Bromoacetaldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-(Formylmethyl)glutathione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aldophosphamide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C07645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-Glutathionyl cyclophosphamide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nitrile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrogen cyanide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ester sulfate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ubiquinone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ubiquinol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salicylate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acyl-carrier protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farnesylcysteine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2E,6E)-farnesal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malonyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Ketoglutaryl-[acp] methyl ester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Hydroxyglutaryl-[acp] methyl ester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Ketopimeloyl-[acp] methyl ester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Hydroxypimeloyl-[acp] methyl ester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanoclavine-I aldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dihydrochanoclavine-I aldehyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-dehydroshikimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C02637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferricytochrome c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferrocytochrome c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-dehydroquinate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Oxododecanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Oxotetradecanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexadecanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Oxostearoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Hydroxyoctadecanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">butyrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glycolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-(2E,6E)-farnesyl-L-cysteine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tributyrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2-dibutyrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propionyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acetyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malonyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-guanidinobutanamide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-guanidinobutanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ceramide-1 (C26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ethanolamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2R,3R)-2,3-dihydroxy-3-methylpentanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C06007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethanolamine phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mannosylinositol phosphorylceramide B (C26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mannose-1D-myo-inositol 1-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ceramide-2 (C26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-3-Hydroxydodecanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3R)-3-Hydroxytetradecanoyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Oxohexadecanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3R)-3-Hydroxypalmitoyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-oxoacyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3R)-3-Hydroxybutanoyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octadecanoyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octadecenoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linolenoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmitoylglycerone phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-palmitoylglycerol 3-phosphate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dodecanoyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetradecanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-hydroxymyristoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha-L-arabinan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C02474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-Acetyl-D-glucosaminylphosphatidylinositol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3beta-Hydroxy-Delta5-steroid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C03836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Oxo-Delta5-steroid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C01034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexadecenoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-phosphoglycolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(S)-methylmalonyl-CoA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C00683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-2,3-Dihydroxy-3-methylpentanoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-oxooctanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acetoacetyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-oxohexanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(R)-3-Hydroxyhexanoyl-[acp]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C05747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3R)-3-Hydroxyoctanoyl-[acyl-carrier protein]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C04620</t>
+  </si>
+  <si>
     <t xml:space="preserve">(S)-lactate</t>
   </si>
   <si>
     <t xml:space="preserve">C00186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDP-N-acetyl-D-glucosamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coenzyme A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acetyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-adenosyl-L-methionine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-acyl-sn-glycerol 3-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDP-mannose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDP-4-dehydro-6-deoxy-alpha-D-mannose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dolichyl diphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acylglycerone phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chitin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-3-methyl-2-oxobutanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fatty acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2S)-2-hydroxycarboxylate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C15565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-Oxo acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-Acylglycerol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C02112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,3-dihydroxy-2,3-dihydrobenzoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5'-adenylyl sulfate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sulfate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(1),P(4)-bis(5'-adenosyl) tetraphosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isochorismate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,2-Diacyl-sn-glycerol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B00002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-Acetyl-D-glucosaminide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">digalacturonate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C02273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choline phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">serotonin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-Methyltetrahydrofolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-methoxytryptamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menaquinone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-S-Glutathione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C02320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dolichyl phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protein asparagine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolichyl diphosphooligosaccharide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glycoprotein with the oligosaccharide chain attached by N-glycosyl linkage to protein L-asparagine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-Alkyl-sn-glycero-3-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O-alkylglycerone phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-2,3-dihydroxy-3-methylbutanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-Acetyl-D-glucosaminyldiphosphodolichol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N,N'-diacetylchitobiosyldiphosphodolichol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">demethylmenaquinone-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-hydroxy-3-methyl-2-oxobutanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-Nitronaphthalene-7,8-oxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-Nitro-7-glutathionyl-8-hydroxy-7,8-dihydronaphthalene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-Nitronaphthalene-5,6-oxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-Nitro-5-hydroxy-6-glutathionyl-5,6-dihydronaphthalene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bromobenzene-2,3-epoxide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,3-Dihydro-2-S-glutathionyl-3-hydroxy bromobenzene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benzo[a]pyrene-7,8-dihydrodiol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,8-Dihydro-7-hydroxy-8-S-glutathionyl-benzo[a]pyrene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chloroacetyl chloride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-(2-Chloroacetyl)glutathione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C06790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCVG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,2-dibromoethane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glutathione episulfonium ion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydrogen bromide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C13645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-Bromoacetaldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-(Formylmethyl)glutathione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C14871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aldophosphamide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C07645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-Glutathionyl cyclophosphamide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nitrile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydrogen cyanide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ester sulfate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ubiquinone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ubiquinol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salicylate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acyl-carrier protein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farnesylcysteine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C19691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2E,6E)-farnesal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malonyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Ketoglutaryl-[acp] methyl ester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Hydroxyglutaryl-[acp] methyl ester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Ketopimeloyl-[acp] methyl ester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Hydroxypimeloyl-[acp] methyl ester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanoclavine-I aldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dihydrochanoclavine-I aldehyde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C21897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-dehydroshikimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C02637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferricytochrome c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferrocytochrome c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-dehydroquinate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Oxododecanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Oxotetradecanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexadecanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Oxostearoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Hydroxyoctadecanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">butyrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glycolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-(2E,6E)-farnesyl-L-cysteine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tributyrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,2-dibutyrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propionyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acetyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">malonyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-guanidinobutanamide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-guanidinobutanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ceramide-1 (C26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ethanolamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2R,3R)-2,3-dihydroxy-3-methylpentanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C06007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethanolamine phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mannosylinositol phosphorylceramide B (C26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mannose-1D-myo-inositol 1-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ceramide-2 (C26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-3-Hydroxydodecanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3R)-3-Hydroxytetradecanoyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Oxohexadecanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3R)-3-Hydroxypalmitoyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-oxoacyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3R)-3-Hydroxybutanoyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octadecanoyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octadecenoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linolenoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmitoylglycerone phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-palmitoylglycerol 3-phosphate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dodecanoyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tetradecanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-hydroxymyristoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alpha-L-arabinan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C02474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-Acetyl-D-glucosaminylphosphatidylinositol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3beta-Hydroxy-Delta5-steroid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Oxo-Delta5-steroid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexadecenoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-phosphoglycolate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(S)-methylmalonyl-CoA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C00683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-2,3-Dihydroxy-3-methylpentanoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-oxooctanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acetoacetyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-oxohexanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(R)-3-Hydroxyhexanoyl-[acp]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3R)-3-Hydroxyoctanoyl-[acyl-carrier protein]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04620</t>
   </si>
 </sst>
 </file>
@@ -1759,296 +1756,294 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>88</v>
-      </c>
-      <c r="B67" t="s">
-        <v>89</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B68" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71"/>
+        <v>101</v>
+      </c>
+      <c r="B71" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="B75" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B83" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>111</v>
-      </c>
-      <c r="B84" t="s">
-        <v>112</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B85" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="B86" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87">
@@ -2061,308 +2056,310 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88"/>
+        <v>119</v>
+      </c>
+      <c r="B88" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>121</v>
-      </c>
-      <c r="B92" t="s">
-        <v>122</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="B92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B93" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B94" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B95" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>125</v>
-      </c>
-      <c r="B96"/>
+        <v>60</v>
+      </c>
+      <c r="B96" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B98" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B99" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="B100" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B102" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B103" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B104" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>138</v>
-      </c>
-      <c r="B105" t="s">
-        <v>139</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="B105"/>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B106" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B107" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B108" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>125</v>
-      </c>
-      <c r="B109"/>
+        <v>150</v>
+      </c>
+      <c r="B109" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B112" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B113" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B114" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B115" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B116" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B117" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B119" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B120" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B121" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="B122" t="s">
-        <v>155</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B123" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B124" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="B125" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="B126" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127">
@@ -2375,1068 +2372,1024 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="B128" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>74</v>
-      </c>
-      <c r="B129" t="s">
-        <v>75</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="B129"/>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B130" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>162</v>
-      </c>
-      <c r="B131" t="s">
-        <v>163</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="B131"/>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="B132" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>164</v>
-      </c>
-      <c r="B133"/>
+        <v>167</v>
+      </c>
+      <c r="B133" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B134" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>125</v>
-      </c>
-      <c r="B135"/>
+        <v>171</v>
+      </c>
+      <c r="B135" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B136" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B137" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B138" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B139" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B140" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B142" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B143" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B144" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B145" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B146" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B147" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B148" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B149" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B150" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B151" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B152" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B153" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B154" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B155" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>207</v>
+        <v>111</v>
       </c>
       <c r="B156" t="s">
-        <v>208</v>
+        <v>112</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B157" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B158" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B159" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>113</v>
+        <v>219</v>
       </c>
       <c r="B160" t="s">
-        <v>114</v>
+        <v>220</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B161" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B162" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B163" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B164" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B165" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B166" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B167" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B168" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B169" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B170" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B171" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B172" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B173" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B174" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B175" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B176" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>237</v>
+        <v>97</v>
       </c>
       <c r="B177" t="s">
-        <v>238</v>
+        <v>98</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B178" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="B179" t="s">
-        <v>244</v>
+        <v>57</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="B180" t="s">
-        <v>246</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>243</v>
+        <v>39</v>
       </c>
       <c r="B181" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="B182" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>99</v>
+        <v>247</v>
       </c>
       <c r="B183" t="s">
-        <v>100</v>
+        <v>248</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B184" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
       <c r="B185" t="s">
-        <v>57</v>
+        <v>252</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>43</v>
+        <v>253</v>
       </c>
       <c r="B186" t="s">
-        <v>44</v>
+        <v>254</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>39</v>
+        <v>255</v>
       </c>
       <c r="B187" t="s">
-        <v>40</v>
+        <v>256</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="B188" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B189" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B190" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B191" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>255</v>
-      </c>
-      <c r="B192" t="s">
-        <v>256</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="B192"/>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>257</v>
-      </c>
-      <c r="B193" t="s">
-        <v>258</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="B193"/>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>259</v>
-      </c>
-      <c r="B194" t="s">
-        <v>260</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="B194"/>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B195" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>261</v>
-      </c>
-      <c r="B196" t="s">
         <v>262</v>
       </c>
+      <c r="B196"/>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>261</v>
-      </c>
-      <c r="B197" t="s">
-        <v>262</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="B197"/>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B198"/>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B199"/>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>264</v>
+      </c>
+      <c r="B200" t="s">
         <v>265</v>
       </c>
-      <c r="B200"/>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B201" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>264</v>
-      </c>
-      <c r="B202"/>
+        <v>268</v>
+      </c>
+      <c r="B202" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>265</v>
-      </c>
-      <c r="B203"/>
+        <v>270</v>
+      </c>
+      <c r="B203" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>264</v>
-      </c>
-      <c r="B204"/>
+        <v>272</v>
+      </c>
+      <c r="B204" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B205"/>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B206" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B207" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B208" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>272</v>
+        <v>70</v>
       </c>
       <c r="B209" t="s">
-        <v>273</v>
+        <v>71</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>274</v>
-      </c>
-      <c r="B210" t="s">
-        <v>275</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="B210"/>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B211"/>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B212"/>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>278</v>
-      </c>
-      <c r="B213" t="s">
-        <v>279</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="B213"/>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>280</v>
-      </c>
-      <c r="B214" t="s">
-        <v>281</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="B214"/>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B215" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>276</v>
-      </c>
-      <c r="B216"/>
+        <v>286</v>
+      </c>
+      <c r="B216" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="B217" t="s">
-        <v>71</v>
+        <v>289</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>284</v>
-      </c>
-      <c r="B218"/>
+        <v>290</v>
+      </c>
+      <c r="B218" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>285</v>
-      </c>
-      <c r="B219"/>
+        <v>64</v>
+      </c>
+      <c r="B219" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>284</v>
-      </c>
-      <c r="B220"/>
+        <v>62</v>
+      </c>
+      <c r="B220" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>285</v>
-      </c>
-      <c r="B221"/>
+        <v>62</v>
+      </c>
+      <c r="B221" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>286</v>
-      </c>
-      <c r="B222"/>
+        <v>39</v>
+      </c>
+      <c r="B222" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>287</v>
-      </c>
-      <c r="B223" t="s">
-        <v>288</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B223"/>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>289</v>
-      </c>
-      <c r="B224" t="s">
-        <v>290</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B224"/>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B225" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B226" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>64</v>
+        <v>292</v>
       </c>
       <c r="B227" t="s">
-        <v>65</v>
+        <v>293</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="B228" t="s">
-        <v>63</v>
+        <v>295</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>62</v>
+        <v>296</v>
       </c>
       <c r="B229" t="s">
-        <v>63</v>
+        <v>297</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>39</v>
+        <v>298</v>
       </c>
       <c r="B230" t="s">
-        <v>40</v>
+        <v>299</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>32</v>
-      </c>
-      <c r="B231"/>
+        <v>300</v>
+      </c>
+      <c r="B231" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>32</v>
-      </c>
-      <c r="B232"/>
+        <v>302</v>
+      </c>
+      <c r="B232" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B233" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B234" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B235" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="B236" t="s">
-        <v>298</v>
+        <v>250</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B237" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B238" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B239" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B240" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B241" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B242" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B243" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="B244" t="s">
-        <v>252</v>
+        <v>318</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B245" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B246" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B247" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B248" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B249" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>320</v>
+        <v>41</v>
       </c>
       <c r="B250" t="s">
-        <v>321</v>
+        <v>42</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B251" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B252" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B253" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B254" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B255" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B256" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B257" t="s">
-        <v>281</v>
+        <v>339</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B258" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B259" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>333</v>
-      </c>
-      <c r="B260" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>335</v>
-      </c>
-      <c r="B261" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>337</v>
-      </c>
-      <c r="B262" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>339</v>
-      </c>
-      <c r="B263" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s">
-        <v>333</v>
-      </c>
-      <c r="B264" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s">
         <v>341</v>
-      </c>
-      <c r="B265" t="s">
-        <v>342</v>
       </c>
     </row>
   </sheetData>
